--- a/assets/excel/Order.all3.xlsx
+++ b/assets/excel/Order.all3.xlsx
@@ -5,7 +5,9 @@
   <sheets>
     <sheet state="visible" name="orders" sheetId="1" r:id="rId4"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">orders!$A$1:$A$1000</definedName>
+  </definedNames>
   <calcPr/>
 </workbook>
 </file>
@@ -232,7 +234,7 @@
     <t>2504268QK8ASG7</t>
   </si>
   <si>
-    <t>tolak</t>
+    <t>cancel</t>
   </si>
   <si>
     <t>SPXID053003747474</t>
@@ -658,7 +660,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -674,8 +676,17 @@
     <xf borderId="3" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
+    <xf borderId="3" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="2" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
     <xf borderId="2" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="2" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1212,7 +1223,7 @@
       <c r="A3" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="5" t="s">
         <v>73</v>
       </c>
       <c r="C3" s="4" t="s">
@@ -1361,7 +1372,7 @@
       <c r="A4" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="6" t="s">
         <v>73</v>
       </c>
       <c r="C4" s="3" t="s">
@@ -1507,40 +1518,40 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="C5" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="E5" s="5" t="s">
+      <c r="C5" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="E5" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="F5" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="G5" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="H5" s="5" t="s">
+      <c r="H5" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="I5" s="5" t="s">
+      <c r="I5" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="J5" s="5" t="s">
+      <c r="J5" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="K5" s="5" t="s">
+      <c r="K5" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="L5" s="5" t="s">
+      <c r="L5" s="7" t="s">
         <v>80</v>
       </c>
       <c r="M5" s="3" t="s">
@@ -1582,76 +1593,76 @@
       <c r="Y5" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="Z5" s="5" t="s">
+      <c r="Z5" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="AA5" s="5" t="s">
+      <c r="AA5" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="AB5" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="AC5" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD5" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="AE5" s="5" t="s">
+      <c r="AB5" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="AC5" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="AD5" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE5" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="AF5" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="AG5" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="AH5" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="AI5" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="AJ5" s="5" t="s">
+      <c r="AF5" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="AG5" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="AH5" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="AI5" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="AJ5" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="AK5" s="5" t="s">
+      <c r="AK5" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="AL5" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="AM5" s="5" t="s">
+      <c r="AL5" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="AM5" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="AN5" s="5" t="s">
+      <c r="AN5" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="AO5" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="AP5" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="AQ5" s="5" t="s">
+      <c r="AO5" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="AP5" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="AQ5" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="AR5" s="5" t="s">
+      <c r="AR5" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="AS5" s="5" t="s">
+      <c r="AS5" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="AT5" s="5" t="s">
+      <c r="AT5" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="AU5" s="5" t="s">
+      <c r="AU5" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="AV5" s="5" t="s">
+      <c r="AV5" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="AW5" s="5" t="s">
+      <c r="AW5" s="7" t="s">
         <v>52</v>
       </c>
     </row>
@@ -1954,40 +1965,40 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="7" t="s">
         <v>163</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="C8" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="E8" s="5" t="s">
+      <c r="C8" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="E8" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="F8" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="G8" s="5" t="s">
+      <c r="G8" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="H8" s="5" t="s">
+      <c r="H8" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="I8" s="5" t="s">
+      <c r="I8" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="J8" s="5" t="s">
+      <c r="J8" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="K8" s="5" t="s">
+      <c r="K8" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="L8" s="5" t="s">
+      <c r="L8" s="7" t="s">
         <v>80</v>
       </c>
       <c r="M8" s="4" t="s">
@@ -2029,114 +2040,114 @@
       <c r="Y8" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="Z8" s="5" t="s">
+      <c r="Z8" s="7" t="s">
         <v>171</v>
       </c>
-      <c r="AA8" s="5" t="s">
+      <c r="AA8" s="7" t="s">
         <v>172</v>
       </c>
-      <c r="AB8" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="AC8" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD8" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="AE8" s="5" t="s">
+      <c r="AB8" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="AC8" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="AD8" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE8" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="AF8" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="AG8" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="AH8" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="AI8" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="AJ8" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="AK8" s="5" t="s">
+      <c r="AF8" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="AG8" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="AH8" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="AI8" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="AJ8" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="AK8" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="AL8" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="AM8" s="5" t="s">
+      <c r="AL8" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="AM8" s="7" t="s">
         <v>173</v>
       </c>
-      <c r="AN8" s="5" t="s">
+      <c r="AN8" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="AO8" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="AP8" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="AQ8" s="5" t="s">
+      <c r="AO8" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="AP8" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="AQ8" s="7" t="s">
         <v>174</v>
       </c>
-      <c r="AR8" s="5" t="s">
+      <c r="AR8" s="7" t="s">
         <v>175</v>
       </c>
-      <c r="AS8" s="5" t="s">
+      <c r="AS8" s="7" t="s">
         <v>176</v>
       </c>
-      <c r="AT8" s="5" t="s">
+      <c r="AT8" s="7" t="s">
         <v>177</v>
       </c>
-      <c r="AU8" s="5" t="s">
+      <c r="AU8" s="7" t="s">
         <v>178</v>
       </c>
-      <c r="AV8" s="5" t="s">
+      <c r="AV8" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="AW8" s="5" t="s">
+      <c r="AW8" s="7" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="7" t="s">
         <v>163</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="C9" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="E9" s="5" t="s">
+      <c r="C9" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="E9" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="F9" s="5" t="s">
+      <c r="F9" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="G9" s="5" t="s">
+      <c r="G9" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="H9" s="5" t="s">
+      <c r="H9" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="I9" s="5" t="s">
+      <c r="I9" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="J9" s="5" t="s">
+      <c r="J9" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="K9" s="5" t="s">
+      <c r="K9" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="L9" s="5" t="s">
+      <c r="L9" s="7" t="s">
         <v>80</v>
       </c>
       <c r="M9" s="4" t="s">
@@ -2178,76 +2189,76 @@
       <c r="Y9" s="4" t="s">
         <v>187</v>
       </c>
-      <c r="Z9" s="5" t="s">
+      <c r="Z9" s="7" t="s">
         <v>171</v>
       </c>
-      <c r="AA9" s="5" t="s">
+      <c r="AA9" s="7" t="s">
         <v>172</v>
       </c>
-      <c r="AB9" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="AC9" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD9" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="AE9" s="5" t="s">
+      <c r="AB9" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="AC9" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="AD9" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE9" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="AF9" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="AG9" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="AH9" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="AI9" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="AJ9" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="AK9" s="5" t="s">
+      <c r="AF9" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="AG9" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="AH9" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="AI9" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="AJ9" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="AK9" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="AL9" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="AM9" s="5" t="s">
+      <c r="AL9" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="AM9" s="7" t="s">
         <v>173</v>
       </c>
-      <c r="AN9" s="5" t="s">
+      <c r="AN9" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="AO9" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="AP9" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="AQ9" s="5" t="s">
+      <c r="AO9" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="AP9" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="AQ9" s="7" t="s">
         <v>174</v>
       </c>
-      <c r="AR9" s="5" t="s">
+      <c r="AR9" s="7" t="s">
         <v>175</v>
       </c>
-      <c r="AS9" s="5" t="s">
+      <c r="AS9" s="7" t="s">
         <v>176</v>
       </c>
-      <c r="AT9" s="5" t="s">
+      <c r="AT9" s="7" t="s">
         <v>177</v>
       </c>
-      <c r="AU9" s="5" t="s">
+      <c r="AU9" s="7" t="s">
         <v>178</v>
       </c>
-      <c r="AV9" s="5" t="s">
+      <c r="AV9" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="AW9" s="5" t="s">
+      <c r="AW9" s="7" t="s">
         <v>179</v>
       </c>
     </row>
@@ -3231,7 +3242,10 @@
     <row r="996" ht="15.75" customHeight="1"/>
     <row r="997" ht="15.75" customHeight="1"/>
     <row r="998" ht="15.75" customHeight="1"/>
+    <row r="999" ht="15.75" customHeight="1"/>
+    <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
+  <autoFilter ref="$A$1:$A$1000"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>